--- a/results/2026-02-25-Maxsat/Maxsat_improve_infsteps180.xlsx
+++ b/results/2026-02-25-Maxsat/Maxsat_improve_infsteps180.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\maxsattrainscheduling\results\2026-02-25-Maxsat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\maxsattrainscheduling\results\2026-02-25-Maxsat\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5257E828-8C90-48B9-8F35-1E2FD391C632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="7515"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="results_maxsat_ddd_scl_infsteps180" localSheetId="0">Sheet1!$A$1:$Y$73</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,8 +28,8 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="results_maxsat_ddd_scl_infsteps180" type="6" refreshedVersion="5" background="1" saveData="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="results_maxsat_ddd_scl_infsteps180" type="6" refreshedVersion="5" background="1" saveData="1">
     <textPr codePage="437" sourceFile="D:\github\maxsattrainscheduling\results_maxsat_ddd_scl_infsteps180.csv" comma="1">
       <textFields count="25">
         <textField/>
@@ -374,7 +375,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -428,7 +429,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -448,7 +449,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="results_maxsat_ddd_scl_infsteps180" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_maxsat_ddd_scl_infsteps180" connectionId="1" xr16:uid="{00000000-0016-0000-0000-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -713,37 +714,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC73"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="12" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -829,7 +830,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>6.0661829999999898E-3</v>
       </c>
@@ -918,7 +919,7 @@
         <v>10400.977260208332</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5.2936390000000002E-3</v>
       </c>
@@ -995,7 +996,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>8.6760029999999998E-3</v>
       </c>
@@ -1072,7 +1073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4.0008090000000001E-3</v>
       </c>
@@ -1149,7 +1150,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3.6017829999999899E-3</v>
       </c>
@@ -1226,7 +1227,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2.0041019999999998E-3</v>
       </c>
@@ -1303,7 +1304,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2.9374330000000001E-3</v>
       </c>
@@ -1380,7 +1381,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2.0786984000000001E-2</v>
       </c>
@@ -1457,7 +1458,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>6.7192440000000001E-3</v>
       </c>
@@ -1534,7 +1535,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6.8486769999999897E-3</v>
       </c>
@@ -1611,7 +1612,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>8.1758909999999994E-3</v>
       </c>
@@ -1688,7 +1689,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1.00712859999999E-2</v>
       </c>
@@ -1765,7 +1766,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1.9524969999999899E-3</v>
       </c>
@@ -1842,7 +1843,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>9.7400599999999905E-4</v>
       </c>
@@ -1919,7 +1920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1.93024399999999E-3</v>
       </c>
@@ -1996,7 +1997,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>5.27328E-3</v>
       </c>
@@ -2073,7 +2074,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>9.3278199999999995E-4</v>
       </c>
@@ -2150,7 +2151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1.338894E-3</v>
       </c>
@@ -2227,7 +2228,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1.2097436E-2</v>
       </c>
@@ -2304,7 +2305,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>5.5809100000000003E-4</v>
       </c>
@@ -2381,7 +2382,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>4.2527909999999997E-3</v>
       </c>
@@ -2458,7 +2459,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>3.0017969999999901E-3</v>
       </c>
@@ -2535,7 +2536,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>5.8454739999999998E-3</v>
       </c>
@@ -2612,7 +2613,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1.457379E-3</v>
       </c>
@@ -2689,7 +2690,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2.8092649000000001E-2</v>
       </c>
@@ -2766,7 +2767,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1.7109440999999899E-2</v>
       </c>
@@ -2843,7 +2844,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2.0150879999999999E-2</v>
       </c>
@@ -2920,7 +2921,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>6.9466679999999996E-3</v>
       </c>
@@ -2997,7 +2998,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>5.6210510000000002E-3</v>
       </c>
@@ -3074,7 +3075,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>4.2095149999999996E-3</v>
       </c>
@@ -3151,7 +3152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3.3160279999999999E-3</v>
       </c>
@@ -3228,7 +3229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1.4848274370000001</v>
       </c>
@@ -3302,7 +3303,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1.6637241000000001E-2</v>
       </c>
@@ -3379,7 +3380,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>7.9804290000000007E-3</v>
       </c>
@@ -3456,7 +3457,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0.18019849400000901</v>
       </c>
@@ -3530,7 +3531,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0.24115329500000299</v>
       </c>
@@ -3604,7 +3605,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>7.1449699999999996E-3</v>
       </c>
@@ -3681,7 +3682,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1.366482E-3</v>
       </c>
@@ -3758,7 +3759,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1.967211E-3</v>
       </c>
@@ -3835,7 +3836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>8.30106399999999E-3</v>
       </c>
@@ -3912,7 +3913,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>2.940626E-3</v>
       </c>
@@ -3989,7 +3990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1.133228E-3</v>
       </c>
@@ -4066,7 +4067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1.3897133000000001E-2</v>
       </c>
@@ -4143,7 +4144,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1.2205979999999901E-3</v>
       </c>
@@ -4220,7 +4221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2.630603E-3</v>
       </c>
@@ -4297,7 +4298,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1.237515E-3</v>
       </c>
@@ -4374,7 +4375,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1.4784554E-2</v>
       </c>
@@ -4451,7 +4452,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>5.7438239999999998E-3</v>
       </c>
@@ -4528,7 +4529,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2.6222025999999898E-2</v>
       </c>
@@ -4605,7 +4606,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>3.4262104999999897E-2</v>
       </c>
@@ -4682,7 +4683,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1.0995157E-2</v>
       </c>
@@ -4759,7 +4760,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>6.3013260000000003E-3</v>
       </c>
@@ -4836,7 +4837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>6.1711049999999901E-3</v>
       </c>
@@ -4913,7 +4914,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2.754186E-3</v>
       </c>
@@ -4990,7 +4991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2.1076630000000001E-3</v>
       </c>
@@ -5067,7 +5068,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>0.13497313999999899</v>
       </c>
@@ -5144,7 +5145,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1.2034417E-2</v>
       </c>
@@ -5221,7 +5222,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>7.2878179999999997E-3</v>
       </c>
@@ -5298,7 +5299,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>0.20934988700000101</v>
       </c>
@@ -5372,7 +5373,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>0.100748893000002</v>
       </c>
@@ -5446,7 +5447,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1.0704793000000001E-2</v>
       </c>
@@ -5523,7 +5524,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1.3348380000000001E-3</v>
       </c>
@@ -5600,7 +5601,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1.710449E-3</v>
       </c>
@@ -5677,7 +5678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2.1639688000000001E-2</v>
       </c>
@@ -5754,7 +5755,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2.8235280000000001E-3</v>
       </c>
@@ -5831,7 +5832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1.422169E-3</v>
       </c>
@@ -5908,7 +5909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1.8432151000000001E-2</v>
       </c>
@@ -5985,7 +5986,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2.1839889999999999E-3</v>
       </c>
@@ -6062,7 +6063,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>2.2547829999999998E-3</v>
       </c>
@@ -6139,7 +6140,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1.0177809999999999E-3</v>
       </c>
@@ -6216,7 +6217,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1.8985143999999898E-2</v>
       </c>
@@ -6293,7 +6294,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>7.5441375000000005E-2</v>
       </c>
